--- a/VerveStacks_EGY_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_EGY_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EGY_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C46E45B1-3CFF-4A09-B35F-C196ACE18037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8DF62763-C3F6-4B79-A394-365E93140B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1041,6 +1041,60 @@
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
+    <t>distr_solelc_spv_EGY_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_EGY_033</t>
   </si>
   <si>
@@ -1053,6 +1107,66 @@
     <t>connecting solar to buses in cluster 24</t>
   </si>
   <si>
+    <t>distr_solelc_spv_EGY_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_EGY_006</t>
   </si>
   <si>
@@ -1065,48 +1179,6 @@
     <t>connecting solar to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_solelc_spv_EGY_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_EGY_036</t>
   </si>
   <si>
@@ -1119,6 +1191,24 @@
     <t>connecting solar to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_solelc_spv_EGY_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_EGY_005</t>
   </si>
   <si>
@@ -1149,52 +1239,16 @@
     <t>connecting solar to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_solelc_spv_EGY_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
+    <t>distr_solelc_spv_EGY_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_EGY_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
   </si>
   <si>
     <t>distr_solelc_spv_EGY_003</t>
@@ -1209,60 +1263,6 @@
     <t>connecting solar to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_solelc_spv_EGY_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_EGY_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
@@ -1275,40 +1275,76 @@
     <t>e_w218893323-220_EGY,e_w216224349-220_EGY</t>
   </si>
   <si>
+    <t>e_w103998472-220_EGY,e_w1219565424-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w127261542-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w218893323-220_EGY,e_w120516782-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w120516782-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w97721460-500_EGY</t>
+  </si>
+  <si>
+    <t>e_w117393191-500_EGY,e_w1219565424-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w98663495-500_EGY,e_w127261542-220_EGY,e_w218893323-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w263290997-220_EGY,e_w117393191-500_EGY</t>
+  </si>
+  <si>
+    <t>e_w117393191-500_EGY,e_w98663495-500_EGY</t>
+  </si>
+  <si>
     <t>e_w263365083-220_EGY,e_w117393191-500_EGY</t>
   </si>
   <si>
     <t>e_w127261542-220_EGY,e_w218893323-220_EGY,e_w120516782-220_EGY</t>
   </si>
   <si>
+    <t>e_w1219565424-220_EGY,e_w127261542-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w117393191-500_EGY,e_w98663495-500_EGY,e_w218893323-220_EGY,e_w115491527-220_EGY,e_w216224349-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w263290997-220_EGY,e_w130435119-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w219295621-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w98663495-500_EGY</t>
+  </si>
+  <si>
+    <t>e_w216224349-220_EGY,e_w115491527-220_EGY,e_w99788079-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w117393191-500_EGY,e_w263365083-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w1219565424-220_EGY</t>
+  </si>
+  <si>
     <t>e_w117393191-500_EGY,e_w103998472-220_EGY,e_w1219565424-220_EGY</t>
   </si>
   <si>
-    <t>e_w216224349-220_EGY,e_w115491527-220_EGY,e_w99788079-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w103998472-220_EGY,e_w1219565424-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w127261542-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w218893323-220_EGY,e_w120516782-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w120516782-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w97721460-500_EGY</t>
-  </si>
-  <si>
     <t>e_w117393191-500_EGY,e_w1219565424-220_EGY,e_w98663495-500_EGY,e_w127261542-220_EGY</t>
   </si>
   <si>
     <t>e_w130435119-220_EGY,e_w115491527-220_EGY,e_w99788079-220_EGY</t>
   </si>
   <si>
-    <t>e_w1219565424-220_EGY</t>
+    <t>e_w263365083-220_EGY,e_w263290997-220_EGY</t>
+  </si>
+  <si>
+    <t>e_w263290997-220_EGY,e_w130435119-220_EGY,e_w219295621-220_EGY</t>
   </si>
   <si>
     <t>e_w263290997-220_EGY,e_w130435119-220_EGY,e_w115491527-220_EGY</t>
@@ -1320,43 +1356,73 @@
     <t>e_w120516782-220_EGY,e_w218893323-220_EGY</t>
   </si>
   <si>
-    <t>e_w98663495-500_EGY</t>
-  </si>
-  <si>
-    <t>e_w117393191-500_EGY,e_w1219565424-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w98663495-500_EGY,e_w127261542-220_EGY,e_w218893323-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w263290997-220_EGY,e_w117393191-500_EGY</t>
-  </si>
-  <si>
-    <t>e_w117393191-500_EGY,e_w98663495-500_EGY</t>
-  </si>
-  <si>
-    <t>e_w1219565424-220_EGY,e_w127261542-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w263365083-220_EGY,e_w263290997-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w263290997-220_EGY,e_w130435119-220_EGY,e_w219295621-220_EGY</t>
-  </si>
-  <si>
     <t>e_w216224349-220_EGY,e_w97721460-500_EGY,e_w218893323-220_EGY</t>
   </si>
   <si>
-    <t>e_w117393191-500_EGY,e_w98663495-500_EGY,e_w218893323-220_EGY,e_w115491527-220_EGY,e_w216224349-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w263290997-220_EGY,e_w130435119-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w219295621-220_EGY</t>
-  </si>
-  <si>
-    <t>e_w117393191-500_EGY,e_w263365083-220_EGY</t>
+    <t>distr_wonelc_won_EGY_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
   </si>
   <si>
     <t>distr_wonelc_won_EGY_007</t>
@@ -1365,6 +1431,78 @@
     <t>connecting wind onshore to buses in cluster 7</t>
   </si>
   <si>
+    <t>distr_wonelc_won_EGY_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_EGY_027</t>
   </si>
   <si>
@@ -1377,28 +1515,16 @@
     <t>connecting wind onshore to buses in cluster 31</t>
   </si>
   <si>
-    <t>distr_wonelc_won_EGY_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
+    <t>distr_wonelc_won_EGY_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_EGY_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
   </si>
   <si>
     <t>distr_wonelc_won_EGY_034</t>
@@ -1449,60 +1575,12 @@
     <t>connecting wind onshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wonelc_won_EGY_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_EGY_011</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
-    <t>distr_wonelc_won_EGY_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_EGY_026</t>
   </si>
   <si>
@@ -1515,82 +1593,52 @@
     <t>connecting wind onshore to buses in cluster 30</t>
   </si>
   <si>
-    <t>distr_wonelc_won_EGY_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_EGY_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
+    <t>elc_won_EGY_025</t>
+  </si>
+  <si>
+    <t>e_w117393191-500_EGY</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_029</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_010</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_038</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_013</t>
+  </si>
+  <si>
+    <t>e_w117393191-500_EGY,e_w98663495-500_EGY,e_w218893323-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_019</t>
+  </si>
+  <si>
+    <t>e_w127261542-220_EGY,e_w218893323-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_008</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_001</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_009</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_035</t>
+  </si>
+  <si>
+    <t>e_w98663495-500_EGY,e_w218893323-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_021</t>
+  </si>
+  <si>
+    <t>e_w216224349-220_EGY,e_w97721460-500_EGY</t>
   </si>
   <si>
     <t>elc_won_EGY_007</t>
@@ -1599,25 +1647,73 @@
     <t>e_w263365083-220_EGY,e_w117393191-500_EGY,e_w263290997-220_EGY</t>
   </si>
   <si>
+    <t>elc_won_EGY_033</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_012</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_036</t>
+  </si>
+  <si>
+    <t>e_w127261542-220_EGY,e_w98663495-500_EGY,e_w218893323-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_017</t>
+  </si>
+  <si>
+    <t>e_w1219565424-220_EGY,e_w127261542-220_EGY,e_w120516782-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_003</t>
+  </si>
+  <si>
+    <t>e_w130435119-220_EGY,e_w99788079-220_EGY,e_w219295621-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_002</t>
+  </si>
+  <si>
+    <t>e_w99788079-220_EGY,e_w219295621-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_015</t>
+  </si>
+  <si>
+    <t>e_w115491527-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_005</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_022</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_006</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_028</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_014</t>
+  </si>
+  <si>
+    <t>e_w216224349-220_EGY,e_w99788079-220_EGY,e_w97721460-500_EGY</t>
+  </si>
+  <si>
     <t>elc_won_EGY_027</t>
   </si>
   <si>
     <t>elc_won_EGY_031</t>
   </si>
   <si>
-    <t>elc_won_EGY_022</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_025</t>
-  </si>
-  <si>
-    <t>e_w117393191-500_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_029</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_010</t>
+    <t>elc_won_EGY_020</t>
+  </si>
+  <si>
+    <t>elc_won_EGY_004</t>
+  </si>
+  <si>
+    <t>e_w130435119-220_EGY,e_w115491527-220_EGY,e_w219295621-220_EGY</t>
   </si>
   <si>
     <t>elc_won_EGY_034</t>
@@ -1653,45 +1749,9 @@
     <t>e_w218893323-220_EGY,e_w97721460-500_EGY</t>
   </si>
   <si>
-    <t>elc_won_EGY_008</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_001</t>
-  </si>
-  <si>
     <t>elc_won_EGY_011</t>
   </si>
   <si>
-    <t>elc_won_EGY_038</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_013</t>
-  </si>
-  <si>
-    <t>e_w117393191-500_EGY,e_w98663495-500_EGY,e_w218893323-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_019</t>
-  </si>
-  <si>
-    <t>e_w127261542-220_EGY,e_w218893323-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_009</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_035</t>
-  </si>
-  <si>
-    <t>e_w98663495-500_EGY,e_w218893323-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_021</t>
-  </si>
-  <si>
-    <t>e_w216224349-220_EGY,e_w97721460-500_EGY</t>
-  </si>
-  <si>
     <t>elc_won_EGY_026</t>
   </si>
   <si>
@@ -1701,64 +1761,40 @@
     <t>elc_won_EGY_030</t>
   </si>
   <si>
-    <t>elc_won_EGY_006</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_028</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_014</t>
-  </si>
-  <si>
-    <t>e_w216224349-220_EGY,e_w99788079-220_EGY,e_w97721460-500_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_033</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_012</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_036</t>
-  </si>
-  <si>
-    <t>e_w127261542-220_EGY,e_w98663495-500_EGY,e_w218893323-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_017</t>
-  </si>
-  <si>
-    <t>e_w1219565424-220_EGY,e_w127261542-220_EGY,e_w120516782-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_003</t>
-  </si>
-  <si>
-    <t>e_w130435119-220_EGY,e_w99788079-220_EGY,e_w219295621-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_002</t>
-  </si>
-  <si>
-    <t>e_w99788079-220_EGY,e_w219295621-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_020</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_004</t>
-  </si>
-  <si>
-    <t>e_w130435119-220_EGY,e_w115491527-220_EGY,e_w219295621-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_015</t>
-  </si>
-  <si>
-    <t>e_w115491527-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_won_EGY_005</t>
+    <t>distr_wofelc_wof_EGY_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_EGY_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_EGY_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_EGY_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_EGY_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_EGY_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
     <t>distr_wofelc_wof_EGY_004</t>
@@ -1779,64 +1815,52 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_EGY_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_EGY_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_EGY_012</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_EGY_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_EGY_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_EGY_007</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_EGY_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_EGY_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_EGY_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_EGY_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_EGY_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_EGY_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
+    <t>elc_wof_EGY_011</t>
+  </si>
+  <si>
+    <t>elc_wof_EGY_010</t>
+  </si>
+  <si>
+    <t>elc_wof_EGY_003</t>
+  </si>
+  <si>
+    <t>e_w99788079-220_EGY,e_w216224349-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_wof_EGY_008</t>
+  </si>
+  <si>
+    <t>elc_wof_EGY_005</t>
+  </si>
+  <si>
+    <t>e_w219295621-220_EGY,e_w99788079-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_wof_EGY_013</t>
   </si>
   <si>
     <t>elc_wof_EGY_004</t>
@@ -1854,46 +1878,22 @@
     <t>elc_wof_EGY_006</t>
   </si>
   <si>
-    <t>elc_wof_EGY_008</t>
-  </si>
-  <si>
-    <t>elc_wof_EGY_005</t>
-  </si>
-  <si>
-    <t>e_w219295621-220_EGY,e_w99788079-220_EGY</t>
-  </si>
-  <si>
     <t>elc_wof_EGY_012</t>
   </si>
   <si>
+    <t>elc_wof_EGY_001</t>
+  </si>
+  <si>
+    <t>e_w216224349-220_EGY</t>
+  </si>
+  <si>
+    <t>elc_wof_EGY_009</t>
+  </si>
+  <si>
+    <t>e_w127261542-220_EGY,e_w120516782-220_EGY</t>
+  </si>
+  <si>
     <t>elc_wof_EGY_007</t>
-  </si>
-  <si>
-    <t>elc_wof_EGY_009</t>
-  </si>
-  <si>
-    <t>e_w127261542-220_EGY,e_w120516782-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_wof_EGY_011</t>
-  </si>
-  <si>
-    <t>elc_wof_EGY_010</t>
-  </si>
-  <si>
-    <t>elc_wof_EGY_003</t>
-  </si>
-  <si>
-    <t>e_w99788079-220_EGY,e_w216224349-220_EGY</t>
-  </si>
-  <si>
-    <t>elc_wof_EGY_013</t>
-  </si>
-  <si>
-    <t>elc_wof_EGY_001</t>
-  </si>
-  <si>
-    <t>e_w216224349-220_EGY</t>
   </si>
   <si>
     <t>e_won_EGY_001</t>
@@ -7033,7 +7033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6A67E0-CF76-4B3E-880C-E281F8921AAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D389B388-8FC6-4CDA-A64A-0D71F714B85A}">
   <dimension ref="B9:BD49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7313,10 +7313,10 @@
         <v>489</v>
       </c>
       <c r="AO11">
-        <v>0.99286967685912142</v>
+        <v>0.97499427436081509</v>
       </c>
       <c r="AP11">
-        <v>130.72259091610712</v>
+        <v>458.43830338505609</v>
       </c>
       <c r="AR11" t="s">
         <v>297</v>
@@ -7346,13 +7346,13 @@
         <v>570</v>
       </c>
       <c r="BB11" t="s">
-        <v>571</v>
+        <v>382</v>
       </c>
       <c r="BC11">
-        <v>0.99595939579278592</v>
+        <v>0.99608088951124507</v>
       </c>
       <c r="BD11">
-        <v>74.077743798924104</v>
+        <v>71.85035896050627</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7456,13 +7456,13 @@
         <v>490</v>
       </c>
       <c r="AN12" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="AO12">
-        <v>0.99594859585576734</v>
+        <v>0.99008488012481999</v>
       </c>
       <c r="AP12">
-        <v>74.275742644265065</v>
+        <v>181.77719771163297</v>
       </c>
       <c r="AR12" t="s">
         <v>297</v>
@@ -7489,16 +7489,16 @@
         <v>546</v>
       </c>
       <c r="BA12" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="BB12" t="s">
-        <v>573</v>
+        <v>385</v>
       </c>
       <c r="BC12">
-        <v>0.99674789271186581</v>
+        <v>0.99469886179826295</v>
       </c>
       <c r="BD12">
-        <v>59.621966949126438</v>
+        <v>97.18753369851197</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -7563,16 +7563,16 @@
         <v>304</v>
       </c>
       <c r="Y13" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="Z13" t="s">
         <v>382</v>
       </c>
       <c r="AA13">
-        <v>0.99367168138570572</v>
+        <v>0.99590121579576196</v>
       </c>
       <c r="AB13">
-        <v>116.01917459539435</v>
+        <v>75.144377077696873</v>
       </c>
       <c r="AD13" t="s">
         <v>297</v>
@@ -7602,13 +7602,13 @@
         <v>491</v>
       </c>
       <c r="AN13" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AO13">
-        <v>0.98301540620183814</v>
+        <v>0.99004283227598866</v>
       </c>
       <c r="AP13">
-        <v>311.3842196329673</v>
+        <v>182.54807494020739</v>
       </c>
       <c r="AR13" t="s">
         <v>297</v>
@@ -7635,16 +7635,16 @@
         <v>548</v>
       </c>
       <c r="BA13" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="BB13" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="BC13">
-        <v>0.99457658163375595</v>
+        <v>0.99839741386765135</v>
       </c>
       <c r="BD13">
-        <v>99.429336714475255</v>
+        <v>29.380745759724935</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7709,16 +7709,16 @@
         <v>306</v>
       </c>
       <c r="Y14" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="Z14" t="s">
         <v>383</v>
       </c>
       <c r="AA14">
-        <v>0.99915483990102039</v>
+        <v>0.99889219700710985</v>
       </c>
       <c r="AB14">
-        <v>15.494601814626803</v>
+        <v>20.309721536319785</v>
       </c>
       <c r="AD14" t="s">
         <v>297</v>
@@ -7748,13 +7748,13 @@
         <v>492</v>
       </c>
       <c r="AN14" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="AO14">
-        <v>0.99769521668575056</v>
+        <v>0.98766025661460344</v>
       </c>
       <c r="AP14">
-        <v>42.254360761239127</v>
+        <v>226.22862873227024</v>
       </c>
       <c r="AR14" t="s">
         <v>297</v>
@@ -7781,10 +7781,10 @@
         <v>550</v>
       </c>
       <c r="BA14" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="BB14" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="BC14">
         <v>0.99525347829094968</v>
@@ -7855,16 +7855,16 @@
         <v>308</v>
       </c>
       <c r="Y15" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="Z15" t="s">
         <v>384</v>
       </c>
       <c r="AA15">
-        <v>0.97486820482067216</v>
+        <v>0.99950425386021668</v>
       </c>
       <c r="AB15">
-        <v>460.74957828767765</v>
+        <v>9.088679229359883</v>
       </c>
       <c r="AD15" t="s">
         <v>297</v>
@@ -7897,10 +7897,10 @@
         <v>494</v>
       </c>
       <c r="AO15">
-        <v>0.97499427436081509</v>
+        <v>0.99640185989529162</v>
       </c>
       <c r="AP15">
-        <v>458.43830338505609</v>
+        <v>65.965901919653419</v>
       </c>
       <c r="AR15" t="s">
         <v>297</v>
@@ -7927,10 +7927,10 @@
         <v>552</v>
       </c>
       <c r="BA15" t="s">
+        <v>575</v>
+      </c>
+      <c r="BB15" t="s">
         <v>576</v>
-      </c>
-      <c r="BB15" t="s">
-        <v>577</v>
       </c>
       <c r="BC15">
         <v>0.99089936244800603</v>
@@ -8001,16 +8001,16 @@
         <v>310</v>
       </c>
       <c r="Y16" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="Z16" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AA16">
-        <v>0.9846486966208019</v>
+        <v>0.99687640119266907</v>
       </c>
       <c r="AB16">
-        <v>281.44056195196578</v>
+        <v>57.265978134401102</v>
       </c>
       <c r="AD16" t="s">
         <v>297</v>
@@ -8040,13 +8040,13 @@
         <v>495</v>
       </c>
       <c r="AN16" t="s">
-        <v>386</v>
+        <v>496</v>
       </c>
       <c r="AO16">
-        <v>0.99008488012481999</v>
+        <v>0.99942456888749764</v>
       </c>
       <c r="AP16">
-        <v>181.77719771163297</v>
+        <v>10.549570395875852</v>
       </c>
       <c r="AR16" t="s">
         <v>297</v>
@@ -8073,16 +8073,16 @@
         <v>554</v>
       </c>
       <c r="BA16" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="BB16" t="s">
         <v>393</v>
       </c>
       <c r="BC16">
-        <v>0.99769284795311641</v>
+        <v>0.99698678830528309</v>
       </c>
       <c r="BD16">
-        <v>42.297787526198668</v>
+        <v>55.242214403142619</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8147,16 +8147,16 @@
         <v>312</v>
       </c>
       <c r="Y17" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="Z17" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="AA17">
-        <v>0.99218426384428171</v>
+        <v>0.99854092015014972</v>
       </c>
       <c r="AB17">
-        <v>143.28849618816821</v>
+        <v>26.749797247254357</v>
       </c>
       <c r="AD17" t="s">
         <v>297</v>
@@ -8183,16 +8183,16 @@
         <v>422</v>
       </c>
       <c r="AM17" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AN17" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="AO17">
-        <v>0.99004283227598866</v>
+        <v>0.99457901875633581</v>
       </c>
       <c r="AP17">
-        <v>182.54807494020739</v>
+        <v>99.38465613384264</v>
       </c>
       <c r="AR17" t="s">
         <v>297</v>
@@ -8219,16 +8219,16 @@
         <v>556</v>
       </c>
       <c r="BA17" t="s">
+        <v>578</v>
+      </c>
+      <c r="BB17" t="s">
         <v>579</v>
       </c>
-      <c r="BB17" t="s">
-        <v>408</v>
-      </c>
       <c r="BC17">
-        <v>0.99388255470924491</v>
+        <v>0.99595939579278592</v>
       </c>
       <c r="BD17">
-        <v>112.15316366384342</v>
+        <v>74.077743798924104</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8293,16 +8293,16 @@
         <v>314</v>
       </c>
       <c r="Y18" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
       <c r="Z18" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="AA18">
-        <v>0.99753395262242606</v>
+        <v>0.98044745846612325</v>
       </c>
       <c r="AB18">
-        <v>45.210868588855774</v>
+        <v>358.46326145440685</v>
       </c>
       <c r="AD18" t="s">
         <v>297</v>
@@ -8329,16 +8329,16 @@
         <v>424</v>
       </c>
       <c r="AM18" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN18" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="AO18">
-        <v>0.97925287661264049</v>
+        <v>0.99783879693751998</v>
       </c>
       <c r="AP18">
-        <v>380.36392876825732</v>
+        <v>39.622056145466821</v>
       </c>
       <c r="AR18" t="s">
         <v>297</v>
@@ -8371,10 +8371,10 @@
         <v>581</v>
       </c>
       <c r="BC18">
-        <v>0.99604998238339004</v>
+        <v>0.99674789271186581</v>
       </c>
       <c r="BD18">
-        <v>72.416989637848886</v>
+        <v>59.621966949126438</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8439,16 +8439,16 @@
         <v>316</v>
       </c>
       <c r="Y19" t="s">
-        <v>258</v>
+        <v>284</v>
       </c>
       <c r="Z19" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AA19">
-        <v>0.99590121579576196</v>
+        <v>0.99447988216030536</v>
       </c>
       <c r="AB19">
-        <v>75.144377077696873</v>
+        <v>101.20216039440101</v>
       </c>
       <c r="AD19" t="s">
         <v>297</v>
@@ -8475,16 +8475,16 @@
         <v>426</v>
       </c>
       <c r="AM19" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN19" t="s">
-        <v>499</v>
+        <v>406</v>
       </c>
       <c r="AO19">
-        <v>0.98293781343467301</v>
+        <v>0.99606454310458625</v>
       </c>
       <c r="AP19">
-        <v>312.80675369766186</v>
+        <v>72.150043082585043</v>
       </c>
       <c r="AR19" t="s">
         <v>297</v>
@@ -8514,13 +8514,13 @@
         <v>582</v>
       </c>
       <c r="BB19" t="s">
-        <v>386</v>
+        <v>579</v>
       </c>
       <c r="BC19">
-        <v>0.99608088951124507</v>
+        <v>0.99457658163375595</v>
       </c>
       <c r="BD19">
-        <v>71.85035896050627</v>
+        <v>99.429336714475255</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8585,16 +8585,16 @@
         <v>318</v>
       </c>
       <c r="Y20" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="Z20" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AA20">
-        <v>0.99889219700710985</v>
+        <v>0.99371871850748283</v>
       </c>
       <c r="AB20">
-        <v>20.309721536319785</v>
+        <v>115.1568273628157</v>
       </c>
       <c r="AD20" t="s">
         <v>297</v>
@@ -8624,13 +8624,13 @@
         <v>500</v>
       </c>
       <c r="AN20" t="s">
-        <v>401</v>
+        <v>501</v>
       </c>
       <c r="AO20">
-        <v>0.99242743615560192</v>
+        <v>0.99854453431225465</v>
       </c>
       <c r="AP20">
-        <v>138.83033714729854</v>
+        <v>26.683537608665571</v>
       </c>
       <c r="AR20" t="s">
         <v>297</v>
@@ -8660,13 +8660,13 @@
         <v>583</v>
       </c>
       <c r="BB20" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="BC20">
-        <v>0.99469886179826295</v>
+        <v>0.99769284795311641</v>
       </c>
       <c r="BD20">
-        <v>97.18753369851197</v>
+        <v>42.297787526198668</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8731,16 +8731,16 @@
         <v>320</v>
       </c>
       <c r="Y21" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="Z21" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA21">
-        <v>0.99950425386021668</v>
+        <v>0.99513896160089133</v>
       </c>
       <c r="AB21">
-        <v>9.088679229359883</v>
+        <v>89.119037316993314</v>
       </c>
       <c r="AD21" t="s">
         <v>297</v>
@@ -8767,16 +8767,16 @@
         <v>430</v>
       </c>
       <c r="AM21" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AN21" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO21">
-        <v>0.99562821601256868</v>
+        <v>0.99709412771239236</v>
       </c>
       <c r="AP21">
-        <v>80.149373102906665</v>
+        <v>53.27432527280623</v>
       </c>
       <c r="AR21" t="s">
         <v>297</v>
@@ -8809,10 +8809,10 @@
         <v>585</v>
       </c>
       <c r="BC21">
-        <v>0.99839741386765135</v>
+        <v>0.99828786497940292</v>
       </c>
       <c r="BD21">
-        <v>29.380745759724935</v>
+        <v>31.389142044280668</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8877,16 +8877,16 @@
         <v>322</v>
       </c>
       <c r="Y22" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="Z22" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AA22">
-        <v>0.99687640119266907</v>
+        <v>0.99367168138570572</v>
       </c>
       <c r="AB22">
-        <v>57.265978134401102</v>
+        <v>116.01917459539435</v>
       </c>
       <c r="AD22" t="s">
         <v>297</v>
@@ -8913,16 +8913,16 @@
         <v>432</v>
       </c>
       <c r="AM22" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AN22" t="s">
-        <v>389</v>
+        <v>505</v>
       </c>
       <c r="AO22">
-        <v>0.99721868227112154</v>
+        <v>0.99286967685912142</v>
       </c>
       <c r="AP22">
-        <v>50.990825029437481</v>
+        <v>130.72259091610712</v>
       </c>
       <c r="AR22" t="s">
         <v>297</v>
@@ -8952,13 +8952,13 @@
         <v>586</v>
       </c>
       <c r="BB22" t="s">
-        <v>402</v>
+        <v>587</v>
       </c>
       <c r="BC22">
-        <v>0.99698678830528309</v>
+        <v>0.99604998238339004</v>
       </c>
       <c r="BD22">
-        <v>55.242214403142619</v>
+        <v>72.416989637848886</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9023,16 +9023,16 @@
         <v>324</v>
       </c>
       <c r="Y23" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="Z23" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AA23">
-        <v>0.99854092015014972</v>
+        <v>0.99915483990102039</v>
       </c>
       <c r="AB23">
-        <v>26.749797247254357</v>
+        <v>15.494601814626803</v>
       </c>
       <c r="AD23" t="s">
         <v>297</v>
@@ -9059,16 +9059,16 @@
         <v>434</v>
       </c>
       <c r="AM23" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AN23" t="s">
         <v>380</v>
       </c>
       <c r="AO23">
-        <v>0.983339003136948</v>
+        <v>0.98042189002817315</v>
       </c>
       <c r="AP23">
-        <v>305.45160915595284</v>
+        <v>358.93201615015897</v>
       </c>
       <c r="AR23" t="s">
         <v>297</v>
@@ -9095,16 +9095,16 @@
         <v>568</v>
       </c>
       <c r="BA23" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="BB23" t="s">
-        <v>588</v>
+        <v>396</v>
       </c>
       <c r="BC23">
-        <v>0.99828786497940292</v>
+        <v>0.99388255470924491</v>
       </c>
       <c r="BD23">
-        <v>31.389142044280668</v>
+        <v>112.15316366384342</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9169,16 +9169,16 @@
         <v>326</v>
       </c>
       <c r="Y24" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="Z24" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AA24">
-        <v>0.98389757326709382</v>
+        <v>0.98831053875443708</v>
       </c>
       <c r="AB24">
-        <v>295.21115676994617</v>
+        <v>214.30678950198768</v>
       </c>
       <c r="AD24" t="s">
         <v>297</v>
@@ -9205,16 +9205,16 @@
         <v>436</v>
       </c>
       <c r="AM24" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AN24" t="s">
-        <v>402</v>
+        <v>489</v>
       </c>
       <c r="AO24">
-        <v>0.99796848780756553</v>
+        <v>0.99595339933639915</v>
       </c>
       <c r="AP24">
-        <v>37.244390194630974</v>
+        <v>74.18767883268319</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9279,16 +9279,16 @@
         <v>328</v>
       </c>
       <c r="Y25" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="Z25" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA25">
-        <v>0.99593918344116994</v>
+        <v>0.99658621475166509</v>
       </c>
       <c r="AB25">
-        <v>74.448303578551162</v>
+        <v>62.586062886140176</v>
       </c>
       <c r="AD25" t="s">
         <v>297</v>
@@ -9315,16 +9315,16 @@
         <v>438</v>
       </c>
       <c r="AM25" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AN25" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AO25">
-        <v>0.99585101802144804</v>
+        <v>0.99230979301190114</v>
       </c>
       <c r="AP25">
-        <v>76.064669606786566</v>
+        <v>140.98712811514619</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9389,16 +9389,16 @@
         <v>330</v>
       </c>
       <c r="Y26" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="Z26" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="AA26">
-        <v>0.97578919257448515</v>
+        <v>0.99650411795938953</v>
       </c>
       <c r="AB26">
-        <v>443.86480280110607</v>
+        <v>64.091170744525783</v>
       </c>
       <c r="AD26" t="s">
         <v>297</v>
@@ -9425,16 +9425,16 @@
         <v>440</v>
       </c>
       <c r="AM26" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AN26" t="s">
-        <v>407</v>
+        <v>511</v>
       </c>
       <c r="AO26">
-        <v>0.99457901875633581</v>
+        <v>0.99899299279751275</v>
       </c>
       <c r="AP26">
-        <v>99.38465613384264</v>
+        <v>18.46179871226661</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9499,16 +9499,16 @@
         <v>332</v>
       </c>
       <c r="Y27" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="Z27" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AA27">
-        <v>0.99734725364305532</v>
+        <v>0.9973293952782647</v>
       </c>
       <c r="AB27">
-        <v>48.633683210651689</v>
+        <v>48.961086565147021</v>
       </c>
       <c r="AD27" t="s">
         <v>297</v>
@@ -9535,16 +9535,16 @@
         <v>442</v>
       </c>
       <c r="AM27" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="AN27" t="s">
-        <v>408</v>
+        <v>513</v>
       </c>
       <c r="AO27">
-        <v>0.99783879693751998</v>
+        <v>0.99499324321175298</v>
       </c>
       <c r="AP27">
-        <v>39.622056145466821</v>
+        <v>91.790541117862404</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9609,16 +9609,16 @@
         <v>334</v>
       </c>
       <c r="Y28" t="s">
-        <v>267</v>
+        <v>293</v>
       </c>
       <c r="Z28" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AA28">
-        <v>0.99572476715323455</v>
+        <v>0.99444904038232829</v>
       </c>
       <c r="AB28">
-        <v>78.379268857365901</v>
+        <v>101.76759299064801</v>
       </c>
       <c r="AD28" t="s">
         <v>297</v>
@@ -9645,16 +9645,16 @@
         <v>444</v>
       </c>
       <c r="AM28" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="AN28" t="s">
-        <v>395</v>
+        <v>515</v>
       </c>
       <c r="AO28">
-        <v>0.99651697123564165</v>
+        <v>0.99625416611041828</v>
       </c>
       <c r="AP28">
-        <v>63.855527346569112</v>
+        <v>68.673621308997852</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9719,16 +9719,16 @@
         <v>336</v>
       </c>
       <c r="Y29" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="Z29" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="AA29">
-        <v>0.99693563762414594</v>
+        <v>0.99218426384428171</v>
       </c>
       <c r="AB29">
-        <v>56.179976890657493</v>
+        <v>143.28849618816821</v>
       </c>
       <c r="AD29" t="s">
         <v>297</v>
@@ -9755,16 +9755,16 @@
         <v>446</v>
       </c>
       <c r="AM29" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
       <c r="AN29" t="s">
-        <v>382</v>
+        <v>517</v>
       </c>
       <c r="AO29">
-        <v>0.98766025661460344</v>
+        <v>0.99804346119092568</v>
       </c>
       <c r="AP29">
-        <v>226.22862873227024</v>
+        <v>35.869878166361715</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9829,16 +9829,16 @@
         <v>338</v>
       </c>
       <c r="Y30" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="Z30" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AA30">
-        <v>0.99683915336458406</v>
+        <v>0.99753395262242606</v>
       </c>
       <c r="AB30">
-        <v>57.948854982625846</v>
+        <v>45.210868588855774</v>
       </c>
       <c r="AD30" t="s">
         <v>297</v>
@@ -9865,16 +9865,16 @@
         <v>448</v>
       </c>
       <c r="AM30" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="AN30" t="s">
-        <v>513</v>
+        <v>396</v>
       </c>
       <c r="AO30">
-        <v>0.99640185989529162</v>
+        <v>0.99086772337116769</v>
       </c>
       <c r="AP30">
-        <v>65.965901919653419</v>
+        <v>167.42507152859298</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9939,16 +9939,16 @@
         <v>340</v>
       </c>
       <c r="Y31" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="Z31" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA31">
-        <v>0.99444904038232829</v>
+        <v>0.99357562675717948</v>
       </c>
       <c r="AB31">
-        <v>101.76759299064801</v>
+        <v>117.78017611837716</v>
       </c>
       <c r="AD31" t="s">
         <v>297</v>
@@ -9975,16 +9975,16 @@
         <v>450</v>
       </c>
       <c r="AM31" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="AN31" t="s">
-        <v>515</v>
+        <v>381</v>
       </c>
       <c r="AO31">
-        <v>0.99942456888749764</v>
+        <v>0.99769521668575056</v>
       </c>
       <c r="AP31">
-        <v>10.549570395875852</v>
+        <v>42.254360761239127</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10049,16 +10049,16 @@
         <v>342</v>
       </c>
       <c r="Y32" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="Z32" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="AA32">
-        <v>0.98044745846612325</v>
+        <v>0.99872661179086297</v>
       </c>
       <c r="AB32">
-        <v>358.46326145440685</v>
+        <v>23.34545050084521</v>
       </c>
       <c r="AD32" t="s">
         <v>297</v>
@@ -10085,16 +10085,16 @@
         <v>452</v>
       </c>
       <c r="AM32" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AN32" t="s">
-        <v>394</v>
+        <v>380</v>
       </c>
       <c r="AO32">
-        <v>0.99606454310458625</v>
+        <v>0.99412669951476118</v>
       </c>
       <c r="AP32">
-        <v>72.150043082585043</v>
+        <v>107.67717556271087</v>
       </c>
     </row>
     <row r="33" spans="2:42">
@@ -10159,16 +10159,16 @@
         <v>344</v>
       </c>
       <c r="Y33" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Z33" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AA33">
-        <v>0.99447988216030536</v>
+        <v>0.9943669167560808</v>
       </c>
       <c r="AB33">
-        <v>101.20216039440101</v>
+        <v>103.27319280518496</v>
       </c>
       <c r="AD33" t="s">
         <v>297</v>
@@ -10195,16 +10195,16 @@
         <v>454</v>
       </c>
       <c r="AM33" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AN33" t="s">
-        <v>518</v>
+        <v>400</v>
       </c>
       <c r="AO33">
-        <v>0.99854453431225465</v>
+        <v>0.99725335832947681</v>
       </c>
       <c r="AP33">
-        <v>26.683537608665571</v>
+        <v>50.355097292924711</v>
       </c>
     </row>
     <row r="34" spans="2:42">
@@ -10269,16 +10269,16 @@
         <v>346</v>
       </c>
       <c r="Y34" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z34" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AA34">
-        <v>0.99371871850748283</v>
+        <v>0.97486820482067216</v>
       </c>
       <c r="AB34">
-        <v>115.1568273628157</v>
+        <v>460.74957828767765</v>
       </c>
       <c r="AD34" t="s">
         <v>297</v>
@@ -10305,16 +10305,16 @@
         <v>456</v>
       </c>
       <c r="AM34" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="AN34" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AO34">
-        <v>0.99709412771239236</v>
+        <v>0.99817728108013837</v>
       </c>
       <c r="AP34">
-        <v>53.27432527280623</v>
+        <v>33.416513530797559</v>
       </c>
     </row>
     <row r="35" spans="2:42">
@@ -10379,16 +10379,16 @@
         <v>348</v>
       </c>
       <c r="Y35" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="Z35" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="AA35">
-        <v>0.99513896160089133</v>
+        <v>0.9846486966208019</v>
       </c>
       <c r="AB35">
-        <v>89.119037316993314</v>
+        <v>281.44056195196578</v>
       </c>
       <c r="AD35" t="s">
         <v>297</v>
@@ -10415,16 +10415,16 @@
         <v>458</v>
       </c>
       <c r="AM35" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="AN35" t="s">
-        <v>522</v>
+        <v>382</v>
       </c>
       <c r="AO35">
-        <v>0.97729426649715556</v>
+        <v>0.99594859585576734</v>
       </c>
       <c r="AP35">
-        <v>416.27178088548152</v>
+        <v>74.275742644265065</v>
       </c>
     </row>
     <row r="36" spans="2:42">
@@ -10489,16 +10489,16 @@
         <v>350</v>
       </c>
       <c r="Y36" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="Z36" t="s">
         <v>402</v>
       </c>
       <c r="AA36">
-        <v>0.99879196722376351</v>
+        <v>0.98389757326709382</v>
       </c>
       <c r="AB36">
-        <v>22.147267564335049</v>
+        <v>295.21115676994617</v>
       </c>
       <c r="AD36" t="s">
         <v>297</v>
@@ -10525,16 +10525,16 @@
         <v>460</v>
       </c>
       <c r="AM36" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AN36" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AO36">
-        <v>0.9929303293411601</v>
+        <v>0.98301540620183814</v>
       </c>
       <c r="AP36">
-        <v>129.61062874539911</v>
+        <v>311.3842196329673</v>
       </c>
     </row>
     <row r="37" spans="2:42">
@@ -10599,16 +10599,16 @@
         <v>352</v>
       </c>
       <c r="Y37" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="Z37" t="s">
         <v>403</v>
       </c>
       <c r="AA37">
-        <v>0.99440114110241684</v>
+        <v>0.99593918344116994</v>
       </c>
       <c r="AB37">
-        <v>102.64574645569184</v>
+        <v>74.448303578551162</v>
       </c>
       <c r="AD37" t="s">
         <v>297</v>
@@ -10635,16 +10635,16 @@
         <v>462</v>
       </c>
       <c r="AM37" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN37" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="AO37">
-        <v>0.99412669951476118</v>
+        <v>0.99869533301057312</v>
       </c>
       <c r="AP37">
-        <v>107.67717556271087</v>
+        <v>23.918894806159585</v>
       </c>
     </row>
     <row r="38" spans="2:42">
@@ -10709,16 +10709,16 @@
         <v>354</v>
       </c>
       <c r="Y38" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="Z38" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="AA38">
-        <v>0.99272852147127866</v>
+        <v>0.99879196722376351</v>
       </c>
       <c r="AB38">
-        <v>133.31043969322533</v>
+        <v>22.147267564335049</v>
       </c>
       <c r="AD38" t="s">
         <v>297</v>
@@ -10745,16 +10745,16 @@
         <v>464</v>
       </c>
       <c r="AM38" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="AN38" t="s">
-        <v>393</v>
+        <v>528</v>
       </c>
       <c r="AO38">
-        <v>0.99725335832947681</v>
+        <v>0.99545577417100861</v>
       </c>
       <c r="AP38">
-        <v>50.355097292924711</v>
+        <v>83.310806864841808</v>
       </c>
     </row>
     <row r="39" spans="2:42">
@@ -10819,16 +10819,16 @@
         <v>356</v>
       </c>
       <c r="Y39" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="Z39" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
       <c r="AA39">
-        <v>0.99090451216750186</v>
+        <v>0.99440114110241684</v>
       </c>
       <c r="AB39">
-        <v>166.75061026246621</v>
+        <v>102.64574645569184</v>
       </c>
       <c r="AD39" t="s">
         <v>297</v>
@@ -10855,16 +10855,16 @@
         <v>466</v>
       </c>
       <c r="AM39" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AN39" t="s">
-        <v>527</v>
+        <v>391</v>
       </c>
       <c r="AO39">
-        <v>0.99817728108013837</v>
+        <v>0.97925287661264049</v>
       </c>
       <c r="AP39">
-        <v>33.416513530797559</v>
+        <v>380.36392876825732</v>
       </c>
     </row>
     <row r="40" spans="2:42">
@@ -10929,16 +10929,16 @@
         <v>358</v>
       </c>
       <c r="Y40" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="Z40" t="s">
         <v>405</v>
       </c>
       <c r="AA40">
-        <v>0.99550967885930464</v>
+        <v>0.99272852147127866</v>
       </c>
       <c r="AB40">
-        <v>82.32255424608114</v>
+        <v>133.31043969322533</v>
       </c>
       <c r="AD40" t="s">
         <v>297</v>
@@ -10965,16 +10965,16 @@
         <v>468</v>
       </c>
       <c r="AM40" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AN40" t="s">
-        <v>380</v>
+        <v>531</v>
       </c>
       <c r="AO40">
-        <v>0.98042189002817315</v>
+        <v>0.98293781343467301</v>
       </c>
       <c r="AP40">
-        <v>358.93201615015897</v>
+        <v>312.80675369766186</v>
       </c>
     </row>
     <row r="41" spans="2:42">
@@ -11039,16 +11039,16 @@
         <v>360</v>
       </c>
       <c r="Y41" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Z41" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AA41">
-        <v>0.98272622614343641</v>
+        <v>0.97578919257448515</v>
       </c>
       <c r="AB41">
-        <v>316.68585403699831</v>
+        <v>443.86480280110607</v>
       </c>
       <c r="AD41" t="s">
         <v>297</v>
@@ -11075,16 +11075,16 @@
         <v>470</v>
       </c>
       <c r="AM41" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AN41" t="s">
-        <v>494</v>
+        <v>390</v>
       </c>
       <c r="AO41">
-        <v>0.99595339933639915</v>
+        <v>0.99242743615560192</v>
       </c>
       <c r="AP41">
-        <v>74.18767883268319</v>
+        <v>138.83033714729854</v>
       </c>
     </row>
     <row r="42" spans="2:42">
@@ -11149,16 +11149,16 @@
         <v>362</v>
       </c>
       <c r="Y42" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="Z42" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AA42">
-        <v>0.99093655882362075</v>
+        <v>0.99734725364305532</v>
       </c>
       <c r="AB42">
-        <v>166.16308823361996</v>
+        <v>48.633683210651689</v>
       </c>
       <c r="AD42" t="s">
         <v>297</v>
@@ -11185,16 +11185,16 @@
         <v>472</v>
       </c>
       <c r="AM42" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AN42" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AO42">
-        <v>0.99230979301190114</v>
+        <v>0.99562821601256868</v>
       </c>
       <c r="AP42">
-        <v>140.98712811514619</v>
+        <v>80.149373102906665</v>
       </c>
     </row>
     <row r="43" spans="2:42">
@@ -11259,16 +11259,16 @@
         <v>364</v>
       </c>
       <c r="Y43" t="s">
-        <v>285</v>
+        <v>267</v>
       </c>
       <c r="Z43" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="AA43">
-        <v>0.98831053875443708</v>
+        <v>0.99572476715323455</v>
       </c>
       <c r="AB43">
-        <v>214.30678950198768</v>
+        <v>78.379268857365901</v>
       </c>
       <c r="AD43" t="s">
         <v>297</v>
@@ -11295,16 +11295,16 @@
         <v>474</v>
       </c>
       <c r="AM43" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AN43" t="s">
-        <v>533</v>
+        <v>385</v>
       </c>
       <c r="AO43">
-        <v>0.99899299279751275</v>
+        <v>0.99721868227112154</v>
       </c>
       <c r="AP43">
-        <v>18.46179871226661</v>
+        <v>50.990825029437481</v>
       </c>
     </row>
     <row r="44" spans="2:42">
@@ -11369,16 +11369,16 @@
         <v>366</v>
       </c>
       <c r="Y44" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Z44" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AA44">
-        <v>0.99658621475166509</v>
+        <v>0.99693563762414594</v>
       </c>
       <c r="AB44">
-        <v>62.586062886140176</v>
+        <v>56.179976890657493</v>
       </c>
       <c r="AD44" t="s">
         <v>297</v>
@@ -11405,16 +11405,16 @@
         <v>476</v>
       </c>
       <c r="AM44" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AN44" t="s">
-        <v>535</v>
+        <v>380</v>
       </c>
       <c r="AO44">
-        <v>0.99499324321175298</v>
+        <v>0.983339003136948</v>
       </c>
       <c r="AP44">
-        <v>91.790541117862404</v>
+        <v>305.45160915595284</v>
       </c>
     </row>
     <row r="45" spans="2:42">
@@ -11479,16 +11479,16 @@
         <v>368</v>
       </c>
       <c r="Y45" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="Z45" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA45">
-        <v>0.99650411795938953</v>
+        <v>0.99683915336458406</v>
       </c>
       <c r="AB45">
-        <v>64.091170744525783</v>
+        <v>57.948854982625846</v>
       </c>
       <c r="AD45" t="s">
         <v>297</v>
@@ -11515,16 +11515,16 @@
         <v>478</v>
       </c>
       <c r="AM45" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AN45" t="s">
-        <v>537</v>
+        <v>393</v>
       </c>
       <c r="AO45">
-        <v>0.99625416611041828</v>
+        <v>0.99796848780756553</v>
       </c>
       <c r="AP45">
-        <v>68.673621308997852</v>
+        <v>37.244390194630974</v>
       </c>
     </row>
     <row r="46" spans="2:42">
@@ -11589,16 +11589,16 @@
         <v>370</v>
       </c>
       <c r="Y46" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="Z46" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="AA46">
-        <v>0.9973293952782647</v>
+        <v>0.98272622614343641</v>
       </c>
       <c r="AB46">
-        <v>48.961086565147021</v>
+        <v>316.68585403699831</v>
       </c>
       <c r="AD46" t="s">
         <v>297</v>
@@ -11628,13 +11628,13 @@
         <v>538</v>
       </c>
       <c r="AN46" t="s">
-        <v>383</v>
+        <v>539</v>
       </c>
       <c r="AO46">
-        <v>0.99869533301057312</v>
+        <v>0.99585101802144804</v>
       </c>
       <c r="AP46">
-        <v>23.918894806159585</v>
+        <v>76.064669606786566</v>
       </c>
     </row>
     <row r="47" spans="2:42">
@@ -11699,16 +11699,16 @@
         <v>372</v>
       </c>
       <c r="Y47" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="Z47" t="s">
-        <v>409</v>
+        <v>390</v>
       </c>
       <c r="AA47">
-        <v>0.99357562675717948</v>
+        <v>0.99093655882362075</v>
       </c>
       <c r="AB47">
-        <v>117.78017611837716</v>
+        <v>166.16308823361996</v>
       </c>
       <c r="AD47" t="s">
         <v>297</v>
@@ -11735,16 +11735,16 @@
         <v>482</v>
       </c>
       <c r="AM47" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AN47" t="s">
-        <v>540</v>
+        <v>407</v>
       </c>
       <c r="AO47">
-        <v>0.99545577417100861</v>
+        <v>0.99651697123564165</v>
       </c>
       <c r="AP47">
-        <v>83.310806864841808</v>
+        <v>63.855527346569112</v>
       </c>
     </row>
     <row r="48" spans="2:42">
@@ -11809,16 +11809,16 @@
         <v>374</v>
       </c>
       <c r="Y48" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="Z48" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="AA48">
-        <v>0.99872661179086297</v>
+        <v>0.99090451216750186</v>
       </c>
       <c r="AB48">
-        <v>23.34545050084521</v>
+        <v>166.75061026246621</v>
       </c>
       <c r="AD48" t="s">
         <v>297</v>
@@ -11851,10 +11851,10 @@
         <v>542</v>
       </c>
       <c r="AO48">
-        <v>0.99804346119092568</v>
+        <v>0.97729426649715556</v>
       </c>
       <c r="AP48">
-        <v>35.869878166361715</v>
+        <v>416.27178088548152</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -11919,16 +11919,16 @@
         <v>376</v>
       </c>
       <c r="Y49" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="Z49" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="AA49">
-        <v>0.9943669167560808</v>
+        <v>0.99550967885930464</v>
       </c>
       <c r="AB49">
-        <v>103.27319280518496</v>
+        <v>82.32255424608114</v>
       </c>
       <c r="AD49" t="s">
         <v>297</v>
@@ -11958,13 +11958,13 @@
         <v>543</v>
       </c>
       <c r="AN49" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="AO49">
-        <v>0.99086772337116769</v>
+        <v>0.9929303293411601</v>
       </c>
       <c r="AP49">
-        <v>167.42507152859298</v>
+        <v>129.61062874539911</v>
       </c>
     </row>
   </sheetData>
@@ -11973,7 +11973,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D2DE230-98D0-49CF-B29A-83E590A033F2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B476A667-459D-4878-BF2D-97B3A3CF0AA5}">
   <dimension ref="B9:Z49"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12085,7 +12085,7 @@
         <v>589</v>
       </c>
       <c r="K11" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="L11">
         <v>4.576445128356033</v>
@@ -12118,7 +12118,7 @@
         <v>667</v>
       </c>
       <c r="X11" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="Y11">
         <v>5.7735000000000003</v>
@@ -12153,7 +12153,7 @@
         <v>591</v>
       </c>
       <c r="K12" t="s">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="L12">
         <v>17.090633243201445</v>
@@ -12186,7 +12186,7 @@
         <v>669</v>
       </c>
       <c r="X12" t="s">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="Y12">
         <v>1.7737499999999999</v>
@@ -12221,7 +12221,7 @@
         <v>593</v>
       </c>
       <c r="K13" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="L13">
         <v>30.898534797988123</v>
@@ -12254,7 +12254,7 @@
         <v>671</v>
       </c>
       <c r="X13" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
       <c r="Y13">
         <v>7.3470000000000004</v>
@@ -12289,7 +12289,7 @@
         <v>595</v>
       </c>
       <c r="K14" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="L14">
         <v>25.811566296705735</v>
@@ -12322,7 +12322,7 @@
         <v>673</v>
       </c>
       <c r="X14" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="Y14">
         <v>21.452999999999999</v>
@@ -12357,7 +12357,7 @@
         <v>597</v>
       </c>
       <c r="K15" t="s">
-        <v>543</v>
+        <v>518</v>
       </c>
       <c r="L15">
         <v>23.055923007486331</v>
@@ -12390,7 +12390,7 @@
         <v>675</v>
       </c>
       <c r="X15" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="Y15">
         <v>20.765250000000002</v>
@@ -12425,7 +12425,7 @@
         <v>599</v>
       </c>
       <c r="K16" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="L16">
         <v>54.989492924928747</v>
@@ -12458,7 +12458,7 @@
         <v>677</v>
       </c>
       <c r="X16" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="Y16">
         <v>32.553750000000001</v>
@@ -12493,7 +12493,7 @@
         <v>601</v>
       </c>
       <c r="K17" t="s">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="L17">
         <v>103.61039663602075</v>
@@ -12526,7 +12526,7 @@
         <v>679</v>
       </c>
       <c r="X17" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="Y17">
         <v>20.706</v>
@@ -12561,7 +12561,7 @@
         <v>603</v>
       </c>
       <c r="K18" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
       <c r="L18">
         <v>64.274491549456684</v>
@@ -12594,7 +12594,7 @@
         <v>681</v>
       </c>
       <c r="X18" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="Y18">
         <v>27.207750000000001</v>
@@ -12629,7 +12629,7 @@
         <v>605</v>
       </c>
       <c r="K19" t="s">
-        <v>516</v>
+        <v>499</v>
       </c>
       <c r="L19">
         <v>82.61836165608527</v>
@@ -12662,7 +12662,7 @@
         <v>683</v>
       </c>
       <c r="X19" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="Y19">
         <v>14.126250000000001</v>
@@ -12697,7 +12697,7 @@
         <v>607</v>
       </c>
       <c r="K20" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="L20">
         <v>59.935739041542519</v>
@@ -12730,7 +12730,7 @@
         <v>685</v>
       </c>
       <c r="X20" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="Y20">
         <v>28.477499999999999</v>
@@ -12765,7 +12765,7 @@
         <v>609</v>
       </c>
       <c r="K21" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="L21">
         <v>44.977725623955543</v>
@@ -12798,7 +12798,7 @@
         <v>687</v>
       </c>
       <c r="X21" t="s">
-        <v>582</v>
+        <v>570</v>
       </c>
       <c r="Y21">
         <v>11.24775</v>
@@ -12833,7 +12833,7 @@
         <v>611</v>
       </c>
       <c r="K22" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="L22">
         <v>22.730801787350369</v>
@@ -12866,7 +12866,7 @@
         <v>689</v>
       </c>
       <c r="X22" t="s">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="Y22">
         <v>7.5134999999999996</v>
@@ -12901,7 +12901,7 @@
         <v>613</v>
       </c>
       <c r="K23" t="s">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="L23">
         <v>39.276732601242294</v>
@@ -12934,7 +12934,7 @@
         <v>691</v>
       </c>
       <c r="X23" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="Y23">
         <v>23.138249999999999</v>
@@ -12969,7 +12969,7 @@
         <v>615</v>
       </c>
       <c r="K24" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="L24">
         <v>43.420210910839671</v>
@@ -13004,7 +13004,7 @@
         <v>617</v>
       </c>
       <c r="K25" t="s">
-        <v>541</v>
+        <v>516</v>
       </c>
       <c r="L25">
         <v>25.887004667578061</v>
@@ -13039,7 +13039,7 @@
         <v>619</v>
       </c>
       <c r="K26" t="s">
-        <v>501</v>
+        <v>533</v>
       </c>
       <c r="L26">
         <v>38.24129251402173</v>
@@ -13074,7 +13074,7 @@
         <v>621</v>
       </c>
       <c r="K27" t="s">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="L27">
         <v>4.1169547379845621</v>
@@ -13109,7 +13109,7 @@
         <v>623</v>
       </c>
       <c r="K28" t="s">
-        <v>505</v>
+        <v>537</v>
       </c>
       <c r="L28">
         <v>20.761923008846804</v>
@@ -13144,7 +13144,7 @@
         <v>625</v>
       </c>
       <c r="K29" t="s">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="L29">
         <v>14.57810076358094</v>
@@ -13179,7 +13179,7 @@
         <v>627</v>
       </c>
       <c r="K30" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="L30">
         <v>14.360150467260283</v>
@@ -13214,7 +13214,7 @@
         <v>629</v>
       </c>
       <c r="K31" t="s">
-        <v>519</v>
+        <v>502</v>
       </c>
       <c r="L31">
         <v>12.964537206203417</v>
@@ -13249,7 +13249,7 @@
         <v>631</v>
       </c>
       <c r="K32" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="L32">
         <v>30.896194863683213</v>
@@ -13284,7 +13284,7 @@
         <v>633</v>
       </c>
       <c r="K33" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="L33">
         <v>5.6422005826382176</v>
@@ -13319,7 +13319,7 @@
         <v>635</v>
       </c>
       <c r="K34" t="s">
-        <v>506</v>
+        <v>538</v>
       </c>
       <c r="L34">
         <v>22.719989139495095</v>
@@ -13354,7 +13354,7 @@
         <v>637</v>
       </c>
       <c r="K35" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="L35">
         <v>38.97939492678357</v>
@@ -13389,7 +13389,7 @@
         <v>639</v>
       </c>
       <c r="K36" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="L36">
         <v>38.099488347958484</v>
@@ -13424,7 +13424,7 @@
         <v>641</v>
       </c>
       <c r="K37" t="s">
-        <v>490</v>
+        <v>524</v>
       </c>
       <c r="L37">
         <v>14.876694985862025</v>
@@ -13459,7 +13459,7 @@
         <v>643</v>
       </c>
       <c r="K38" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="L38">
         <v>13.45055940453603</v>
@@ -13494,7 +13494,7 @@
         <v>645</v>
       </c>
       <c r="K39" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="L39">
         <v>50.989244226423629</v>
@@ -13529,7 +13529,7 @@
         <v>647</v>
       </c>
       <c r="K40" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="L40">
         <v>12.035320188057462</v>
@@ -13564,7 +13564,7 @@
         <v>649</v>
       </c>
       <c r="K41" t="s">
-        <v>491</v>
+        <v>525</v>
       </c>
       <c r="L41">
         <v>22.903265854425744</v>
@@ -13599,7 +13599,7 @@
         <v>651</v>
       </c>
       <c r="K42" t="s">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="L42">
         <v>31.03069548845038</v>
@@ -13634,7 +13634,7 @@
         <v>653</v>
       </c>
       <c r="K43" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="L43">
         <v>20.274230032990229</v>
@@ -13669,7 +13669,7 @@
         <v>655</v>
       </c>
       <c r="K44" t="s">
-        <v>497</v>
+        <v>529</v>
       </c>
       <c r="L44">
         <v>36.30904323582736</v>
@@ -13704,7 +13704,7 @@
         <v>657</v>
       </c>
       <c r="K45" t="s">
-        <v>517</v>
+        <v>500</v>
       </c>
       <c r="L45">
         <v>23.277630853320172</v>
@@ -13739,7 +13739,7 @@
         <v>659</v>
       </c>
       <c r="K46" t="s">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="L46">
         <v>42.306544536473055</v>
@@ -13774,7 +13774,7 @@
         <v>661</v>
       </c>
       <c r="K47" t="s">
-        <v>498</v>
+        <v>530</v>
       </c>
       <c r="L47">
         <v>53.875781613985843</v>
@@ -13809,7 +13809,7 @@
         <v>663</v>
       </c>
       <c r="K48" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="L48">
         <v>34.884638950888053</v>
@@ -13844,7 +13844,7 @@
         <v>665</v>
       </c>
       <c r="K49" t="s">
-        <v>500</v>
+        <v>532</v>
       </c>
       <c r="L49">
         <v>56.293737537935385</v>
@@ -13859,7 +13859,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2609BD46-B946-42CF-84E0-2980906C57BD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{581D4764-E4A7-43D0-82BB-004EB450DFC7}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
